--- a/data/3.meta_data/basic_info/26_02_01_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/26_02_01_basic_info.xlsx
@@ -527,9 +527,14 @@
           <t>0095</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0095a</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,7 +544,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Experiental features of volunteering predict changes in college studentsâ€™ social, emotional, and behavioral skills</t>
+          <t>Experiental features of volunteering predict changes in college students' social, emotional, and behavioral skills</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -577,7 +582,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>volunteering</t>
+          <t>volunteering; skilldevelopment</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">

--- a/data/3.meta_data/basic_info/26_02_01_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/26_02_01_basic_info.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.1016/j.jrp.2026.104705</t>
+          <t>https://doi.org/10.1016/j.jrp.2026.104705</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
